--- a/InputData/indst/EoDfIP/Elasticities of Demand for Industrial Products.xlsx
+++ b/InputData/indst/EoDfIP/Elasticities of Demand for Industrial Products.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="23127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="23530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeff-nonadmin\Dropbox (Energy InNovation)\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CodeRepositories\eps-us\InputData\indst\EoDfIP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9838DB3E-7439-47D3-9F3C-3145A30A468E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22524823-0D3A-4448-8DBE-2DA7964E966A}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1485" yWindow="915" windowWidth="24090" windowHeight="16245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3810" yWindow="135" windowWidth="23805" windowHeight="15630" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="104">
   <si>
     <t>Resources for the Future</t>
   </si>
@@ -222,9 +222,6 @@
     <t>Government excluding electricity</t>
   </si>
   <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
     <t>Notes</t>
   </si>
   <si>
@@ -246,24 +243,6 @@
     <t>https://media.rff.org/documents/RFF-DP-08-37.pdf</t>
   </si>
   <si>
-    <t>Natural gas and petroleum systems</t>
-  </si>
-  <si>
-    <t>Iron and steel</t>
-  </si>
-  <si>
-    <t>Chemicals</t>
-  </si>
-  <si>
-    <t>Other industries</t>
-  </si>
-  <si>
-    <t>Cement and other carbonates</t>
-  </si>
-  <si>
-    <t>Water + waste</t>
-  </si>
-  <si>
     <t>Unit: dimensionless (elasticity)</t>
   </si>
   <si>
@@ -313,6 +292,81 @@
   </si>
   <si>
     <t>for these particular data.</t>
+  </si>
+  <si>
+    <t>agriculture and forestry 01T03</t>
+  </si>
+  <si>
+    <t>coal mining 05</t>
+  </si>
+  <si>
+    <t>oil and gas extraction 06</t>
+  </si>
+  <si>
+    <t>other mining and quarrying 07T08</t>
+  </si>
+  <si>
+    <t>food beverage and tobacco 10T12</t>
+  </si>
+  <si>
+    <t>textiles apparel and leather 13T15</t>
+  </si>
+  <si>
+    <t>wood products 16</t>
+  </si>
+  <si>
+    <t>pulp paper and printing 17T18</t>
+  </si>
+  <si>
+    <t>refined petroleum and coke 19</t>
+  </si>
+  <si>
+    <t>chemicals 20</t>
+  </si>
+  <si>
+    <t>rubber and plastic products 22</t>
+  </si>
+  <si>
+    <t>glass and glass products 231</t>
+  </si>
+  <si>
+    <t>cement and other nonmetallic minerals 239</t>
+  </si>
+  <si>
+    <t>iron and steel 241</t>
+  </si>
+  <si>
+    <t>other metals 242</t>
+  </si>
+  <si>
+    <t>metal products except machinery and vehicles 25</t>
+  </si>
+  <si>
+    <t>computers and electronics 26</t>
+  </si>
+  <si>
+    <t>appliances and electrical equipment 27</t>
+  </si>
+  <si>
+    <t>other machinery 28</t>
+  </si>
+  <si>
+    <t>road vehicles 29</t>
+  </si>
+  <si>
+    <t>nonroad vehicles 30</t>
+  </si>
+  <si>
+    <t>other manufacturing 31T33</t>
+  </si>
+  <si>
+    <t>energy pipelines and gas processing 352T353</t>
+  </si>
+  <si>
+    <t>water and waste 36T39</t>
+  </si>
+  <si>
+    <t>construction 41T43</t>
   </si>
 </sst>
 </file>
@@ -426,7 +480,7 @@
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -457,6 +511,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -808,15 +863,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -836,47 +891,47 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +953,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
@@ -906,10 +961,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -920,7 +975,7 @@
         <v>-0.81200000000000006</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -931,7 +986,7 @@
         <v>-0.81200000000000006</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -942,7 +997,7 @@
         <v>-0.29599999999999999</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -953,7 +1008,7 @@
         <v>-0.29599999999999999</v>
       </c>
       <c r="C6" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -964,7 +1019,7 @@
         <v>-0.106</v>
       </c>
       <c r="C7" t="s">
-        <v>5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -975,7 +1030,7 @@
         <v>-0.63300000000000001</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -994,7 +1049,7 @@
         <v>-0.56599999999999995</v>
       </c>
       <c r="C10" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -1005,7 +1060,7 @@
         <v>-0.77400000000000002</v>
       </c>
       <c r="C11" t="s">
-        <v>66</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -1016,7 +1071,7 @@
         <v>-0.63800000000000001</v>
       </c>
       <c r="C12" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -1027,7 +1082,7 @@
         <v>-1.139</v>
       </c>
       <c r="C13" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -1038,7 +1093,7 @@
         <v>-2.4180000000000001</v>
       </c>
       <c r="C14" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -1049,7 +1104,7 @@
         <v>-0.69799999999999995</v>
       </c>
       <c r="C15" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -1060,7 +1115,7 @@
         <v>-0.69799999999999995</v>
       </c>
       <c r="C16" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -1071,7 +1126,7 @@
         <v>-0.69799999999999995</v>
       </c>
       <c r="C17" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -1082,7 +1137,7 @@
         <v>-0.69799999999999995</v>
       </c>
       <c r="C18" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -1093,7 +1148,7 @@
         <v>-0.69799999999999995</v>
       </c>
       <c r="C19" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -1104,7 +1159,7 @@
         <v>-7.0999999999999994E-2</v>
       </c>
       <c r="C20" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -1115,7 +1170,7 @@
         <v>-7.0999999999999994E-2</v>
       </c>
       <c r="C21" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -1126,7 +1181,7 @@
         <v>-0.98699999999999999</v>
       </c>
       <c r="C22" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -1137,7 +1192,7 @@
         <v>-0.98699999999999999</v>
       </c>
       <c r="C23" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -1148,7 +1203,7 @@
         <v>-0.98699999999999999</v>
       </c>
       <c r="C24" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -1159,7 +1214,7 @@
         <v>-0.98699999999999999</v>
       </c>
       <c r="C25" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -1170,7 +1225,7 @@
         <v>-0.98699999999999999</v>
       </c>
       <c r="C26" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -1181,7 +1236,7 @@
         <v>-0.98699999999999999</v>
       </c>
       <c r="C27" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -1192,7 +1247,7 @@
         <v>-0.98699999999999999</v>
       </c>
       <c r="C28" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -1203,7 +1258,7 @@
         <v>-0.82699999999999996</v>
       </c>
       <c r="C29" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -1214,7 +1269,7 @@
         <v>-0.82699999999999996</v>
       </c>
       <c r="C30" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -1225,7 +1280,7 @@
         <v>-0.82699999999999996</v>
       </c>
       <c r="C31" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -1236,7 +1291,7 @@
         <v>-0.82699999999999996</v>
       </c>
       <c r="C32" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -1247,7 +1302,7 @@
         <v>-0.82699999999999996</v>
       </c>
       <c r="C33" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -1258,7 +1313,7 @@
         <v>-0.95299999999999996</v>
       </c>
       <c r="C34" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -1269,7 +1324,7 @@
         <v>-0.95299999999999996</v>
       </c>
       <c r="C35" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -1280,7 +1335,7 @@
         <v>-0.95299999999999996</v>
       </c>
       <c r="C36" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -1291,7 +1346,7 @@
         <v>-0.95299999999999996</v>
       </c>
       <c r="C37" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -1302,7 +1357,7 @@
         <v>-0.95299999999999996</v>
       </c>
       <c r="C38" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -1313,7 +1368,7 @@
         <v>-0.505</v>
       </c>
       <c r="C39" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -1324,7 +1379,7 @@
         <v>-1.6619999999999999</v>
       </c>
       <c r="C40" t="s">
-        <v>66</v>
+        <v>97</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -1335,7 +1390,7 @@
         <v>-2.5960000000000001</v>
       </c>
       <c r="C41" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -1346,7 +1401,7 @@
         <v>-2.4849999999999999</v>
       </c>
       <c r="C42" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -1357,7 +1412,7 @@
         <v>-2.4849999999999999</v>
       </c>
       <c r="C43" t="s">
-        <v>66</v>
+        <v>99</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -1368,7 +1423,7 @@
         <v>-1.6619999999999999</v>
       </c>
       <c r="C44" t="s">
-        <v>66</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -1468,7 +1523,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -1476,13 +1531,13 @@
         <v>2</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1753,7 +1808,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="B22" s="15">
         <v>14743</v>
@@ -1851,7 +1906,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B29" s="15">
         <v>4367</v>
@@ -2103,7 +2158,7 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="B47" s="15">
         <v>194732</v>
@@ -2224,91 +2279,244 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.85546875" customWidth="1"/>
+    <col min="1" max="1" width="47.42578125" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="B2" s="11" cm="1">
         <f t="array" ref="B2">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A2),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A2),0)</f>
-        <v>-0.82699999999999996</v>
+        <v>-0.81200000000000006</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="B3" s="11" cm="1">
         <f t="array" ref="B3">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A3),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A3),0)</f>
-        <v>-0.26923600535787917</v>
+        <v>-0.106</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="B4" s="11" cm="1">
         <f t="array" ref="B4">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A4),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A4),0)</f>
-        <v>-0.95299999999999985</v>
+        <v>-0.29599999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="B5" s="11" cm="1">
         <f t="array" ref="B5">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A5),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A5),0)</f>
-        <v>-0.98568388783511685</v>
+        <v>-0.63300000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="B6" s="11" cm="1">
         <f t="array" ref="B6">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A6),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A6),0)</f>
-        <v>-0.106</v>
+        <v>-0.63800000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="B7" s="11" cm="1">
         <f t="array" ref="B7">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A7),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A7),0)</f>
-        <v>0</v>
+        <v>-1.6823913135674904</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="B8" s="11" cm="1">
         <f t="array" ref="B8">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A8),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A8),0)</f>
-        <v>-0.81200000000000006</v>
+        <v>-0.69799999999999995</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="B9" s="11" cm="1">
         <f t="array" ref="B9">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A9),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A9),0)</f>
-        <v>-1.2596118059082353</v>
+        <v>-0.69799999999999995</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B10" s="11" cm="1">
+        <f t="array" ref="B10">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A10),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A10),0)</f>
+        <v>-7.0999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>88</v>
+      </c>
+      <c r="B11" s="11" cm="1">
+        <f t="array" ref="B11">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A11),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A11),0)</f>
+        <v>-0.98699999999999988</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>89</v>
+      </c>
+      <c r="B12" s="11" cm="1">
+        <f t="array" ref="B12">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A12),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A12),0)</f>
+        <v>-0.98528503405534762</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" s="18">
+        <f>B14</f>
+        <v>-0.82699999999999985</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>91</v>
+      </c>
+      <c r="B14" s="11" cm="1">
+        <f t="array" ref="B14">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A14),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A14),0)</f>
+        <v>-0.82699999999999985</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>92</v>
+      </c>
+      <c r="B15" s="11" cm="1">
+        <f t="array" ref="B15">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A15),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A15),0)</f>
+        <v>-0.95299999999999985</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>93</v>
+      </c>
+      <c r="B16" s="11" cm="1">
+        <f t="array" ref="B16">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A16),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A16),0)</f>
+        <v>-0.95300000000000007</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17" s="11" cm="1">
+        <f t="array" ref="B17">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A17),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A17),0)</f>
+        <v>-0.505</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>95</v>
+      </c>
+      <c r="B18" s="11" cm="1">
+        <f t="array" ref="B18">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A18),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A18),0)</f>
+        <v>-2.5960000000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B19" s="18">
+        <f>B18</f>
+        <v>-2.5960000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>97</v>
+      </c>
+      <c r="B20" s="11" cm="1">
+        <f t="array" ref="B20">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A20),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A20),0)</f>
+        <v>-1.6619999999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>98</v>
+      </c>
+      <c r="B21" s="11" cm="1">
+        <f t="array" ref="B21">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A21),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A21),0)</f>
+        <v>-2.4849999999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>99</v>
+      </c>
+      <c r="B22" s="11" cm="1">
+        <f t="array" ref="B22">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A22),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A22),0)</f>
+        <v>-2.4849999999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>100</v>
+      </c>
+      <c r="B23" s="11" cm="1">
+        <f t="array" ref="B23">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A23),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A23),0)</f>
+        <v>-1.6619999999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>101</v>
+      </c>
+      <c r="B24" s="11" cm="1">
+        <f t="array" ref="B24">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A24),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A24),0)</f>
+        <v>-0.56599999999999995</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>102</v>
+      </c>
+      <c r="B25" s="11" cm="1">
+        <f t="array" ref="B25">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A25),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A25),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>103</v>
+      </c>
+      <c r="B26" s="11" cm="1">
+        <f t="array" ref="B26">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A26),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A26),0)</f>
+        <v>-0.77400000000000002</v>
       </c>
     </row>
   </sheetData>

--- a/InputData/indst/EoDfIP/Elasticities of Demand for Industrial Products.xlsx
+++ b/InputData/indst/EoDfIP/Elasticities of Demand for Industrial Products.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="23530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27021"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CodeRepositories\eps-us\InputData\indst\EoDfIP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22524823-0D3A-4448-8DBE-2DA7964E966A}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{22524823-0D3A-4448-8DBE-2DA7964E966A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{709884B1-DCC5-4450-B41B-25CB23C1B2A5}"/>
   <bookViews>
-    <workbookView xWindow="3810" yWindow="135" windowWidth="23805" windowHeight="15630" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3810" yWindow="135" windowWidth="23805" windowHeight="15630" firstSheet="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -18,14 +18,20 @@
     <sheet name="Table A1" sheetId="16" r:id="rId3"/>
     <sheet name="EoDfIP" sheetId="15" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -55,7 +61,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="105">
+  <si>
+    <t>EoDfIP Elasticities of Demand for Industrial Products</t>
+  </si>
+  <si>
+    <t>Sources:</t>
+  </si>
+  <si>
+    <t>Elasticities</t>
+  </si>
   <si>
     <t>Resources for the Future</t>
   </si>
@@ -63,51 +78,120 @@
     <t>Impact of Carbon Price Policies on U.S. Industry</t>
   </si>
   <si>
+    <t>https://media.rff.org/documents/RFF-DP-08-37.pdf</t>
+  </si>
+  <si>
+    <t>Tables A1 and B6</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>To produce weighted average elastiticies (when one EPS industry category includes multiple</t>
+  </si>
+  <si>
+    <t>categories from RFF's document), we weight by output from the same RFF document.</t>
+  </si>
+  <si>
+    <t>Even though these output values are old (2002 data), they are the best ones to use, because they</t>
+  </si>
+  <si>
+    <t>have the same category breakdown as the RFF's elasticities.  This avoids another mapping step and</t>
+  </si>
+  <si>
+    <t>guarantees output quantities to be non-overlapping, which is more important than recency</t>
+  </si>
+  <si>
+    <t>for these particular data.</t>
+  </si>
+  <si>
+    <t>Elasticity of other industries is average of elasticity of rubber and glass</t>
+  </si>
+  <si>
+    <t>Table B6. Demand Elasticity for Output</t>
+  </si>
+  <si>
     <t>Sector</t>
   </si>
   <si>
+    <t>Demand elasticity for output</t>
+  </si>
+  <si>
+    <t>Matching EPS Industry Category</t>
+  </si>
+  <si>
+    <t>Farms</t>
+  </si>
+  <si>
+    <t>agriculture and forestry 01T03</t>
+  </si>
+  <si>
+    <t>Forestry, fishing, etc.</t>
+  </si>
+  <si>
     <t>Oil mining</t>
   </si>
   <si>
+    <t>oil and gas extraction 06</t>
+  </si>
+  <si>
     <t>Gas mining</t>
   </si>
   <si>
     <t>Coal mining</t>
   </si>
   <si>
+    <t>coal mining 05</t>
+  </si>
+  <si>
+    <t>Other mining activities</t>
+  </si>
+  <si>
+    <t>other mining and quarrying 07T08</t>
+  </si>
+  <si>
+    <t>Electric utilities (including government enterprises)</t>
+  </si>
+  <si>
     <t>Gas utilities</t>
   </si>
   <si>
-    <t>Farms</t>
-  </si>
-  <si>
-    <t>Forestry, fishing, etc.</t>
-  </si>
-  <si>
-    <t>Other mining activities</t>
-  </si>
-  <si>
-    <t>Electric utilities (including government enterprises)</t>
+    <t>energy pipelines and gas processing 352T353</t>
   </si>
   <si>
     <t>Construction</t>
   </si>
   <si>
+    <t>construction 41T43</t>
+  </si>
+  <si>
     <t>Food</t>
   </si>
   <si>
+    <t>food beverage and tobacco 10T12</t>
+  </si>
+  <si>
     <t>Textile</t>
   </si>
   <si>
+    <t>textiles apparel and leather 13T15</t>
+  </si>
+  <si>
     <t>Apparel</t>
   </si>
   <si>
     <t>Wood and furniture</t>
   </si>
   <si>
+    <t>wood products 16</t>
+  </si>
+  <si>
     <t>Pulp mills</t>
   </si>
   <si>
+    <t>pulp paper and printing 17T18</t>
+  </si>
+  <si>
     <t>Paper mills</t>
   </si>
   <si>
@@ -120,12 +204,18 @@
     <t>Refining–LPG</t>
   </si>
   <si>
+    <t>refined petroleum and coke 19</t>
+  </si>
+  <si>
     <t>Refining–other</t>
   </si>
   <si>
     <t>Petrochemical mfg</t>
   </si>
   <si>
+    <t>chemicals 20</t>
+  </si>
+  <si>
     <t>Other basic inorganic chemical mfg.</t>
   </si>
   <si>
@@ -144,12 +234,18 @@
     <t>Other chemical and plastics</t>
   </si>
   <si>
+    <t>rubber and plastic products 22</t>
+  </si>
+  <si>
     <t>Other container manufacturing</t>
   </si>
   <si>
     <t>Cement manufacturing</t>
   </si>
   <si>
+    <t>cement and other nonmetallic minerals 239</t>
+  </si>
+  <si>
     <t>Lime and gypsum product mfg.</t>
   </si>
   <si>
@@ -162,9 +258,15 @@
     <t>Iron and steel mills, ferroalloy mfg.</t>
   </si>
   <si>
+    <t>iron and steel 241</t>
+  </si>
+  <si>
     <t>Alumina refining, primary aluminum</t>
   </si>
   <si>
+    <t>other metals 242</t>
+  </si>
+  <si>
     <t>Ferrous metal foundries</t>
   </si>
   <si>
@@ -177,21 +279,39 @@
     <t>Fabricated metals</t>
   </si>
   <si>
+    <t>metal products except machinery and vehicles 25</t>
+  </si>
+  <si>
     <t>Machinery</t>
   </si>
   <si>
+    <t>other machinery 28</t>
+  </si>
+  <si>
     <t>Computer and electrical equipment</t>
   </si>
   <si>
+    <t>computers and electronics 26</t>
+  </si>
+  <si>
     <t>Motor vehicles</t>
   </si>
   <si>
+    <t>road vehicles 29</t>
+  </si>
+  <si>
     <t>Other transportation equipment</t>
   </si>
   <si>
+    <t>nonroad vehicles 30</t>
+  </si>
+  <si>
     <t>Miscellaneous manufacturing</t>
   </si>
   <si>
+    <t>other manufacturing 31T33</t>
+  </si>
+  <si>
     <t>Trade</t>
   </si>
   <si>
@@ -222,25 +342,25 @@
     <t>Government excluding electricity</t>
   </si>
   <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>Sources:</t>
-  </si>
-  <si>
-    <t>Table B6. Demand Elasticity for Output</t>
-  </si>
-  <si>
-    <t>Demand elasticity for output</t>
-  </si>
-  <si>
-    <t>Elasticities</t>
-  </si>
-  <si>
-    <t>EoDfIP Elasticities of Demand for Industrial Products</t>
-  </si>
-  <si>
-    <t>https://media.rff.org/documents/RFF-DP-08-37.pdf</t>
+    <t>Table A1. Value of Industry and Commodity Output from IO Tables, 2002 (million $)</t>
+  </si>
+  <si>
+    <t>Industry output</t>
+  </si>
+  <si>
+    <t>Commodity output</t>
+  </si>
+  <si>
+    <t>Commodity domestic consumption</t>
+  </si>
+  <si>
+    <t>Petrochemical mfg.</t>
+  </si>
+  <si>
+    <t>Glass container manufacturing</t>
+  </si>
+  <si>
+    <t>Truck transportation</t>
   </si>
   <si>
     <t>Unit: dimensionless (elasticity)</t>
@@ -249,124 +369,13 @@
     <t>Elasticity</t>
   </si>
   <si>
-    <t>Matching EPS Industry Category</t>
-  </si>
-  <si>
-    <t>Petrochemical mfg.</t>
-  </si>
-  <si>
-    <t>Glass container manufacturing</t>
-  </si>
-  <si>
-    <t>Truck transportation</t>
-  </si>
-  <si>
-    <t>Industry output</t>
-  </si>
-  <si>
-    <t>Commodity output</t>
-  </si>
-  <si>
-    <t>Commodity domestic consumption</t>
-  </si>
-  <si>
-    <t>Tables A1 and B6</t>
-  </si>
-  <si>
-    <t>Table A1. Value of Industry and Commodity Output from IO Tables, 2002 (million $)</t>
-  </si>
-  <si>
-    <t>To produce weighted average elastiticies (when one EPS industry category includes multiple</t>
-  </si>
-  <si>
-    <t>categories from RFF's document), we weight by output from the same RFF document.</t>
-  </si>
-  <si>
-    <t>Even though these output values are old (2002 data), they are the best ones to use, because they</t>
-  </si>
-  <si>
-    <t>have the same category breakdown as the RFF's elasticities.  This avoids another mapping step and</t>
-  </si>
-  <si>
-    <t>guarantees output quantities to be non-overlapping, which is more important than recency</t>
-  </si>
-  <si>
-    <t>for these particular data.</t>
-  </si>
-  <si>
-    <t>agriculture and forestry 01T03</t>
-  </si>
-  <si>
-    <t>coal mining 05</t>
-  </si>
-  <si>
-    <t>oil and gas extraction 06</t>
-  </si>
-  <si>
-    <t>other mining and quarrying 07T08</t>
-  </si>
-  <si>
-    <t>food beverage and tobacco 10T12</t>
-  </si>
-  <si>
-    <t>textiles apparel and leather 13T15</t>
-  </si>
-  <si>
-    <t>wood products 16</t>
-  </si>
-  <si>
-    <t>pulp paper and printing 17T18</t>
-  </si>
-  <si>
-    <t>refined petroleum and coke 19</t>
-  </si>
-  <si>
-    <t>chemicals 20</t>
-  </si>
-  <si>
-    <t>rubber and plastic products 22</t>
-  </si>
-  <si>
     <t>glass and glass products 231</t>
   </si>
   <si>
-    <t>cement and other nonmetallic minerals 239</t>
-  </si>
-  <si>
-    <t>iron and steel 241</t>
-  </si>
-  <si>
-    <t>other metals 242</t>
-  </si>
-  <si>
-    <t>metal products except machinery and vehicles 25</t>
-  </si>
-  <si>
-    <t>computers and electronics 26</t>
-  </si>
-  <si>
     <t>appliances and electrical equipment 27</t>
   </si>
   <si>
-    <t>other machinery 28</t>
-  </si>
-  <si>
-    <t>road vehicles 29</t>
-  </si>
-  <si>
-    <t>nonroad vehicles 30</t>
-  </si>
-  <si>
-    <t>other manufacturing 31T33</t>
-  </si>
-  <si>
-    <t>energy pipelines and gas processing 352T353</t>
-  </si>
-  <si>
     <t>water and waste 36T39</t>
-  </si>
-  <si>
-    <t>construction 41T43</t>
   </si>
 </sst>
 </file>
@@ -376,7 +385,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -534,9 +543,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -574,9 +583,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -609,26 +618,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -661,26 +653,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -854,84 +829,89 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.5703125" customWidth="1"/>
     <col min="2" max="2" width="78.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15.75">
       <c r="A3" s="2" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="B4" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="B5" s="3">
         <v>2008</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="B6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="B7" s="9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="B8" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" s="8" customFormat="1">
       <c r="A11" s="8" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>78</v>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -943,7 +923,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C54"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="49.85546875" style="6" customWidth="1"/>
     <col min="2" max="2" width="20.7109375" style="12" customWidth="1"/>
@@ -951,556 +931,556 @@
     <col min="4" max="16384" width="12.5703125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="31.5">
       <c r="A2" s="7" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" s="6" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B3" s="12">
         <v>-0.81200000000000006</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" s="6" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B4" s="12">
         <v>-0.81200000000000006</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="6" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="B5" s="12">
         <v>-0.29599999999999999</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" s="6" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="B6" s="12">
         <v>-0.29599999999999999</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" s="6" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="B7" s="12">
         <v>-0.106</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8" s="6" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="B8" s="12">
         <v>-0.63300000000000001</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9" s="6" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="B9" s="12">
         <v>-0.16</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" s="6" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="B10" s="12">
         <v>-0.56599999999999995</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11" s="6" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="B11" s="12">
         <v>-0.77400000000000002</v>
       </c>
       <c r="C11" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12" s="6" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="B12" s="12">
         <v>-0.63800000000000001</v>
       </c>
       <c r="C12" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13" s="6" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="B13" s="12">
         <v>-1.139</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14" s="6" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="B14" s="12">
         <v>-2.4180000000000001</v>
       </c>
       <c r="C14" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15" s="6" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="B15" s="12">
         <v>-0.69799999999999995</v>
       </c>
       <c r="C15" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16" s="6" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="B16" s="12">
         <v>-0.69799999999999995</v>
       </c>
       <c r="C16" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17" s="6" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="B17" s="12">
         <v>-0.69799999999999995</v>
       </c>
       <c r="C17" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" s="6" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="B18" s="12">
         <v>-0.69799999999999995</v>
       </c>
       <c r="C18" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19" s="6" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="B19" s="12">
         <v>-0.69799999999999995</v>
       </c>
       <c r="C19" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20" s="6" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="B20" s="12">
         <v>-7.0999999999999994E-2</v>
       </c>
       <c r="C20" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21" s="6" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="B21" s="12">
         <v>-7.0999999999999994E-2</v>
       </c>
       <c r="C21" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22" s="6" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="B22" s="12">
         <v>-0.98699999999999999</v>
       </c>
       <c r="C22" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23" s="6" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="B23" s="12">
         <v>-0.98699999999999999</v>
       </c>
       <c r="C23" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
       <c r="A24" s="6" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="B24" s="12">
         <v>-0.98699999999999999</v>
       </c>
       <c r="C24" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
       <c r="A25" s="6" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="B25" s="12">
         <v>-0.98699999999999999</v>
       </c>
       <c r="C25" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
       <c r="A26" s="6" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="B26" s="12">
         <v>-0.98699999999999999</v>
       </c>
       <c r="C26" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
       <c r="A27" s="6" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="B27" s="12">
         <v>-0.98699999999999999</v>
       </c>
       <c r="C27" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
       <c r="A28" s="6" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="B28" s="12">
         <v>-0.98699999999999999</v>
       </c>
       <c r="C28" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
       <c r="A29" s="6" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="B29" s="12">
         <v>-0.82699999999999996</v>
       </c>
       <c r="C29" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
       <c r="A30" s="6" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="B30" s="12">
         <v>-0.82699999999999996</v>
       </c>
       <c r="C30" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
       <c r="A31" s="6" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="B31" s="12">
         <v>-0.82699999999999996</v>
       </c>
       <c r="C31" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
       <c r="A32" s="6" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="B32" s="12">
         <v>-0.82699999999999996</v>
       </c>
       <c r="C32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
       <c r="A33" s="6" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="B33" s="12">
         <v>-0.82699999999999996</v>
       </c>
       <c r="C33" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34" s="6" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="B34" s="12">
         <v>-0.95299999999999996</v>
       </c>
       <c r="C34" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35" s="6" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="B35" s="12">
         <v>-0.95299999999999996</v>
       </c>
       <c r="C35" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
       <c r="A36" s="6" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="B36" s="12">
         <v>-0.95299999999999996</v>
       </c>
       <c r="C36" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37" s="6" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="B37" s="12">
         <v>-0.95299999999999996</v>
       </c>
       <c r="C37" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38" s="6" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="B38" s="12">
         <v>-0.95299999999999996</v>
       </c>
       <c r="C38" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
       <c r="A39" s="6" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="B39" s="12">
         <v>-0.505</v>
       </c>
       <c r="C39" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
       <c r="A40" s="6" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="B40" s="12">
         <v>-1.6619999999999999</v>
       </c>
       <c r="C40" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
       <c r="A41" s="6" t="s">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="B41" s="12">
         <v>-2.5960000000000001</v>
       </c>
       <c r="C41" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
       <c r="A42" s="6" t="s">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="B42" s="12">
         <v>-2.4849999999999999</v>
       </c>
       <c r="C42" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
       <c r="A43" s="6" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="B43" s="12">
         <v>-2.4849999999999999</v>
       </c>
       <c r="C43" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
       <c r="A44" s="6" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="B44" s="12">
         <v>-1.6619999999999999</v>
       </c>
       <c r="C44" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
       <c r="A45" s="6" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="B45" s="12">
         <v>-0.745</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3">
       <c r="A46" s="6" t="s">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="B46" s="12">
         <v>-0.83299999999999996</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3">
       <c r="A47" s="6" t="s">
-        <v>47</v>
+        <v>85</v>
       </c>
       <c r="B47" s="12">
         <v>-0.83299999999999996</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3">
       <c r="A48" s="6" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="B48" s="12">
         <v>-0.83299999999999996</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2">
       <c r="A49" s="6" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="B49" s="12">
         <v>-0.745</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2">
       <c r="A50" s="6" t="s">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="B50" s="12">
         <v>-0.745</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2">
       <c r="A51" s="6" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="B51" s="12">
         <v>-0.745</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2">
       <c r="A52" s="6" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="B52" s="12">
         <v>-0.745</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2">
       <c r="A53" s="6" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="B53" s="12">
         <v>-0.745</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2">
       <c r="A54" s="6" t="s">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="B54" s="12">
         <v>-0.745</v>
@@ -1515,34 +1495,34 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{791C629E-3519-40AD-AC41-C9D8B52341AE}">
   <dimension ref="A1:D54"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="59.42578125" customWidth="1"/>
     <col min="2" max="4" width="20.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15.75">
       <c r="A1" s="5" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="30">
       <c r="A2" s="16" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B3" s="15">
         <v>177337</v>
@@ -1554,9 +1534,9 @@
         <v>168532</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B4" s="15">
         <v>34382</v>
@@ -1568,9 +1548,9 @@
         <v>48460</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="B5" s="15">
         <v>61093</v>
@@ -1582,9 +1562,9 @@
         <v>126146</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="B6" s="15">
         <v>41144</v>
@@ -1596,9 +1576,9 @@
         <v>52569</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="B7" s="15">
         <v>19269</v>
@@ -1610,9 +1590,9 @@
         <v>18881</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="B8" s="15">
         <v>57139</v>
@@ -1624,9 +1604,9 @@
         <v>56813</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="B9" s="15">
         <v>259603</v>
@@ -1638,9 +1618,9 @@
         <v>250852</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="B10" s="15">
         <v>82614</v>
@@ -1652,9 +1632,9 @@
         <v>92926</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="B11" s="15">
         <v>966919</v>
@@ -1666,9 +1646,9 @@
         <v>1031627</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="B12" s="15">
         <v>470396</v>
@@ -1680,9 +1660,9 @@
         <v>486680</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="B13" s="15">
         <v>59670</v>
@@ -1694,9 +1674,9 @@
         <v>62447</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="B14" s="15">
         <v>44078</v>
@@ -1708,9 +1688,9 @@
         <v>133149</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="B15" s="15">
         <v>136132</v>
@@ -1722,9 +1702,9 @@
         <v>164005</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="B16" s="15">
         <v>3443</v>
@@ -1736,9 +1716,9 @@
         <v>5177</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="B17" s="15">
         <v>45319</v>
@@ -1750,9 +1730,9 @@
         <v>52514</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="B18" s="15">
         <v>21095</v>
@@ -1764,9 +1744,9 @@
         <v>19882</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="B19" s="15">
         <v>173273</v>
@@ -1778,9 +1758,9 @@
         <v>145197</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="B20" s="15">
         <v>21023</v>
@@ -1792,9 +1772,9 @@
         <v>15558</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="B21" s="15">
         <v>169836</v>
@@ -1806,9 +1786,9 @@
         <v>191641</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="B22" s="15">
         <v>14743</v>
@@ -1820,9 +1800,9 @@
         <v>18270</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="B23" s="15">
         <v>15177</v>
@@ -1834,9 +1814,9 @@
         <v>17745</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="B24" s="15">
         <v>47573</v>
@@ -1848,9 +1828,9 @@
         <v>47725</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="B25" s="15">
         <v>44832</v>
@@ -1862,9 +1842,9 @@
         <v>38808</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="B26" s="15">
         <v>7651</v>
@@ -1876,9 +1856,9 @@
         <v>12508</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="B27" s="15">
         <v>8239</v>
@@ -1890,9 +1870,9 @@
         <v>9195</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="B28" s="15">
         <v>403058</v>
@@ -1904,9 +1884,9 @@
         <v>448400</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="B29" s="15">
         <v>4367</v>
@@ -1918,9 +1898,9 @@
         <v>4861</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="B30" s="15">
         <v>7058</v>
@@ -1932,9 +1912,9 @@
         <v>8132</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="B31" s="15">
         <v>4900</v>
@@ -1946,9 +1926,9 @@
         <v>4837</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="B32" s="15">
         <v>4834</v>
@@ -1960,9 +1940,9 @@
         <v>4787</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="B33" s="15">
         <v>67020</v>
@@ -1974,9 +1954,9 @@
         <v>74686</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="B34" s="15">
         <v>41942</v>
@@ -1988,9 +1968,9 @@
         <v>62903</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="B35" s="15">
         <v>18765</v>
@@ -2002,9 +1982,9 @@
         <v>22262</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="B36" s="15">
         <v>14700</v>
@@ -2016,9 +1996,9 @@
         <v>14545</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="B37" s="15">
         <v>11420</v>
@@ -2030,9 +2010,9 @@
         <v>11142</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="B38" s="15">
         <v>28403</v>
@@ -2044,9 +2024,9 @@
         <v>29823</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="B39" s="15">
         <v>219291</v>
@@ -2058,9 +2038,9 @@
         <v>225327</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="B40" s="15">
         <v>221635</v>
@@ -2072,9 +2052,9 @@
         <v>228125</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="B41" s="15">
         <v>363578</v>
@@ -2086,9 +2066,9 @@
         <v>466241</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="B42" s="15">
         <v>326173</v>
@@ -2100,9 +2080,9 @@
         <v>450146</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="B43" s="15">
         <v>134524</v>
@@ -2114,9 +2094,9 @@
         <v>105557</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="B44" s="15">
         <v>115134</v>
@@ -2128,9 +2108,9 @@
         <v>158471</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="B45" s="15">
         <v>1850478</v>
@@ -2142,9 +2122,9 @@
         <v>1645222</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="B46" s="15">
         <v>99315</v>
@@ -2156,9 +2136,9 @@
         <v>102147</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="B47" s="15">
         <v>194732</v>
@@ -2170,9 +2150,9 @@
         <v>187881</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="B48" s="15">
         <v>329317</v>
@@ -2184,9 +2164,9 @@
         <v>297242</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="B49" s="15">
         <v>824047</v>
@@ -2198,9 +2178,9 @@
         <v>625365</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="B50" s="15">
         <v>1138654</v>
@@ -2212,9 +2192,9 @@
         <v>1074983</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="B51" s="15">
         <v>1931963</v>
@@ -2226,9 +2206,9 @@
         <v>1953017</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="B52" s="15">
         <v>1710859</v>
@@ -2240,9 +2220,9 @@
         <v>1927957</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="B53" s="15">
         <v>2370176</v>
@@ -2254,9 +2234,9 @@
         <v>2729030</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="B54" s="15">
         <v>2043064</v>
@@ -2280,239 +2260,239 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="47.42578125" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="10" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="B2" s="11" cm="1">
         <f t="array" ref="B2">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A2),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A2),0)</f>
         <v>-0.81200000000000006</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="B3" s="11" cm="1">
         <f t="array" ref="B3">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A3),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A3),0)</f>
         <v>-0.106</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="B4" s="11" cm="1">
         <f t="array" ref="B4">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A4),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A4),0)</f>
         <v>-0.29599999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="B5" s="11" cm="1">
         <f t="array" ref="B5">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A5),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A5),0)</f>
         <v>-0.63300000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>83</v>
+        <v>35</v>
       </c>
       <c r="B6" s="11" cm="1">
         <f t="array" ref="B6">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A6),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A6),0)</f>
         <v>-0.63800000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="B7" s="11" cm="1">
         <f t="array" ref="B7">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A7),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A7),0)</f>
         <v>-1.6823913135674904</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="B8" s="11" cm="1">
         <f t="array" ref="B8">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A8),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A8),0)</f>
         <v>-0.69799999999999995</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="B9" s="11" cm="1">
         <f t="array" ref="B9">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A9),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A9),0)</f>
         <v>-0.69799999999999995</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="B10" s="11" cm="1">
         <f t="array" ref="B10">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A10),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A10),0)</f>
         <v>-7.0999999999999994E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="B11" s="11" cm="1">
         <f t="array" ref="B11">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A11),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A11),0)</f>
         <v>-0.98699999999999988</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="B12" s="11" cm="1">
         <f t="array" ref="B12">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A12),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A12),0)</f>
         <v>-0.98528503405534762</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="B13" s="18">
         <f>B14</f>
         <v>-0.82699999999999985</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="B14" s="11" cm="1">
         <f t="array" ref="B14">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A14),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A14),0)</f>
         <v>-0.82699999999999985</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="B15" s="11" cm="1">
         <f t="array" ref="B15">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A15),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A15),0)</f>
         <v>-0.95299999999999985</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="B16" s="11" cm="1">
         <f t="array" ref="B16">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A16),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A16),0)</f>
         <v>-0.95300000000000007</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="B17" s="11" cm="1">
         <f t="array" ref="B17">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A17),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A17),0)</f>
         <v>-0.505</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="B18" s="11" cm="1">
         <f t="array" ref="B18">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A18),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A18),0)</f>
         <v>-2.5960000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="B19" s="18">
         <f>B18</f>
         <v>-2.5960000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="B20" s="11" cm="1">
         <f t="array" ref="B20">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A20),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A20),0)</f>
         <v>-1.6619999999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="B21" s="11" cm="1">
         <f t="array" ref="B21">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A21),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A21),0)</f>
         <v>-2.4849999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="B22" s="11" cm="1">
         <f t="array" ref="B22">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A22),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A22),0)</f>
         <v>-2.4849999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="B23" s="11" cm="1">
         <f t="array" ref="B23">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A23),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A23),0)</f>
         <v>-1.6619999999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>101</v>
+        <v>31</v>
       </c>
       <c r="B24" s="11" cm="1">
         <f t="array" ref="B24">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A24),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A24),0)</f>
         <v>-0.56599999999999995</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B25" s="11" cm="1">
         <f t="array" ref="B25">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A25),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A25),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>103</v>
+        <v>33</v>
       </c>
       <c r="B26" s="11" cm="1">
         <f t="array" ref="B26">IFERROR(SUMPRODUCT(--('Table B6'!$C$3:$C$54=$A26),'Table B6'!$B$3:$B$54,'Table A1'!$B$3:$B$54)/SUMIFS('Table A1'!$B$3:$B$54,'Table B6'!$C$3:$C$54,$A26),0)</f>
@@ -2523,4 +2503,175 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7abd873f26c83d98889b6bc5171c7cdd">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="295384f30983e71c631053ca9b14fb23" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE11D6B4-EEA4-4964-A775-3679E07F1A12}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E779062F-4392-4758-93E6-B71861FBDB23}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A46470B-BE82-4773-844C-F67C339FBF5E}"/>
 </file>